--- a/dataset_t6_grouped/results2/G3/G3_T6156_W0055F0002T0006Z000C1N24_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G3/G3_T6156_W0055F0002T0006Z000C1N24_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>10.96315611505533</v>
+        <v>1.781512868696492</v>
       </c>
       <c r="D2" t="n">
-        <v>99.73314292218117</v>
+        <v>16.20663572485444</v>
       </c>
       <c r="E2" t="n">
-        <v>37.25586814871814</v>
+        <v>6.054078574166697</v>
       </c>
       <c r="F2" t="n">
-        <v>23.98944593807389</v>
+        <v>3.898284964937007</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>61.96686027543456</v>
+        <v>10.06961479475811</v>
       </c>
       <c r="D3" t="n">
-        <v>66.18232916590743</v>
+        <v>10.75462848945996</v>
       </c>
       <c r="E3" t="n">
-        <v>37.25586814871814</v>
+        <v>6.054078574166697</v>
       </c>
       <c r="F3" t="n">
-        <v>23.98944593807389</v>
+        <v>3.898284964937007</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>57.35362888273723</v>
+        <v>9.319964693444801</v>
       </c>
       <c r="D4" t="n">
-        <v>57.43181156863945</v>
+        <v>9.33266937990391</v>
       </c>
       <c r="E4" t="n">
-        <v>37.25586814871814</v>
+        <v>6.054078574166697</v>
       </c>
       <c r="F4" t="n">
-        <v>23.98944593807389</v>
+        <v>3.898284964937007</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>116.0953460732574</v>
+        <v>18.86549373690432</v>
       </c>
       <c r="D5" t="n">
-        <v>116.1586239764713</v>
+        <v>18.87577639617659</v>
       </c>
       <c r="E5" t="n">
-        <v>37.25586814871814</v>
+        <v>6.054078574166697</v>
       </c>
       <c r="F5" t="n">
-        <v>23.98944593807389</v>
+        <v>3.898284964937007</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
